--- a/class_diagram/users/クラス図_面談予約sys (users)_最新.xlsx
+++ b/class_diagram/users/クラス図_面談予約sys (users)_最新.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20357"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ktc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC5F448-C290-4053-AF89-2C5F4DE0E5F9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{DDC5F448-C290-4053-AF89-2C5F4DE0E5F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C72D9F3-5572-446B-8968-DAF69F875519}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18945" windowHeight="11190" firstSheet="9" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18945" windowHeight="11190" firstSheet="18" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="controller.UserPreServlet" sheetId="1" r:id="rId1"/>
@@ -20,25 +20,41 @@
     <sheet name="controller.UserGetServlet" sheetId="15" r:id="rId5"/>
     <sheet name="dao.UserGetDAO" sheetId="16" r:id="rId6"/>
     <sheet name="controller.UserUpdateServlet" sheetId="17" r:id="rId7"/>
-    <sheet name="dao.UserUpdateDAO" sheetId="18" r:id="rId8"/>
-    <sheet name="controller.UserDeleteServlet" sheetId="19" r:id="rId9"/>
-    <sheet name="dao.UserDeleteDAO" sheetId="20" r:id="rId10"/>
-    <sheet name="controller.LoginServlet" sheetId="26" r:id="rId11"/>
-    <sheet name="dao.LoginDAO" sheetId="7" r:id="rId12"/>
-    <sheet name="controller.ResePreServlet" sheetId="4" r:id="rId13"/>
-    <sheet name="controller.ReseEntryServlet" sheetId="5" r:id="rId14"/>
-    <sheet name="dao.ReseEntryDAO" sheetId="6" r:id="rId15"/>
-    <sheet name="dao.ReseGetDAO" sheetId="8" r:id="rId16"/>
-    <sheet name="controller.ReseGetServlet" sheetId="9" r:id="rId17"/>
-    <sheet name="controller.PastGetServlet" sheetId="21" r:id="rId18"/>
-    <sheet name="dao.PastGetDAO" sheetId="22" r:id="rId19"/>
-    <sheet name="controller.EmailSendPreServlet" sheetId="23" r:id="rId20"/>
-    <sheet name="dao.EmailCheckDAO" sheetId="24" r:id="rId21"/>
+    <sheet name="Sheet1" sheetId="27" r:id="rId8"/>
+    <sheet name="dao.UserUpdateDAO" sheetId="18" r:id="rId9"/>
+    <sheet name="controller.UserDeleteServlet" sheetId="19" r:id="rId10"/>
+    <sheet name="dao.UserDeleteDAO" sheetId="20" r:id="rId11"/>
+    <sheet name="controller.LoginServlet" sheetId="26" r:id="rId12"/>
+    <sheet name="dao.LoginDAO" sheetId="7" r:id="rId13"/>
+    <sheet name="controller.ResePreServlet" sheetId="4" r:id="rId14"/>
+    <sheet name="controller.ReseEntryServlet" sheetId="5" r:id="rId15"/>
+    <sheet name="dao.ReseEntryDAO" sheetId="6" r:id="rId16"/>
+    <sheet name="dao.ReseGetDAO" sheetId="8" r:id="rId17"/>
+    <sheet name="controller.ReseGetAllServlet" sheetId="9" r:id="rId18"/>
+    <sheet name="controller.ReseGetDetailServlet" sheetId="30" r:id="rId19"/>
+    <sheet name="controller.ReseDeleteServlet" sheetId="28" r:id="rId20"/>
+    <sheet name="dao.ReseDeleteDAO" sheetId="29" r:id="rId21"/>
+    <sheet name="controller.PastGetDetailServlet" sheetId="31" r:id="rId22"/>
+    <sheet name="controller.PastGetAllServlet" sheetId="21" r:id="rId23"/>
+    <sheet name="dao.PastGetDAO" sheetId="22" r:id="rId24"/>
+    <sheet name="controller.EmailSendPreServlet" sheetId="23" r:id="rId25"/>
+    <sheet name="dao.EmailCheckDAO" sheetId="24" r:id="rId26"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -55,7 +71,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -169,8 +185,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2325,7 +2339,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>-  reseGet(userID : int) : ArrayList&lt;ReseInfo&gt;</a:t>
+            <a:t>-  reseGetAll(userID : int) : ArrayList&lt;ReseInfo&gt;</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2359,12 +2373,15 @@
               <a:spcPts val="0"/>
             </a:spcAft>
           </a:pPr>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>- reseGetDetail(userID : int, reseID : int) : ArrayList&lt;ReseInfo&gt;</a:t>
+          </a:r>
         </a:p>
         <a:p>
           <a:pPr marL="0" marR="0" indent="0" algn="l">
@@ -2592,7 +2609,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>ReseGetServlet</a:t>
+            <a:t>ReseGetAllServlet</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3010,6 +3027,2503 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{814DEABA-1230-4CA2-802A-E2ECC7E7CAAF}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{15723AC8-7A10-4908-982D-E38FEF435220}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4800600" y="2200275"/>
+          <a:ext cx="5495925" cy="1000125"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>ReseGetDetailServlet</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56DEF463-1504-4668-A459-142B58F9A902}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{814DEABA-1230-4CA2-802A-E2ECC7E7CAAF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4800600" y="3171825"/>
+          <a:ext cx="5486400" cy="4953000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t># doGet(request : HttpServletRequest ,response :  HttpServletResponse) : void</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t># doPost(request : HttpServletRequest ,response :  HttpServletResponse) : void</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95BE081C-E0B0-4C40-8479-E33873DB0DBA}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{15723AC8-7A10-4908-982D-E38FEF435220}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2057400" y="1400175"/>
+          <a:ext cx="5495925" cy="1000125"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>ReseDeleteServlet</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D95BAEC8-F4AD-4EC9-B044-E96FB9245D4A}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{95BE081C-E0B0-4C40-8479-E33873DB0DBA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2057400" y="2400300"/>
+          <a:ext cx="5486400" cy="4953000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t># doGet(request : HttpServletRequest ,response :  HttpServletResponse) : void</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t># doPost(request : HttpServletRequest ,response :  HttpServletResponse) : void</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54A5D636-AB10-4715-8904-91ADDD3CDB92}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{15723AC8-7A10-4908-982D-E38FEF435220}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1371600" y="619125"/>
+          <a:ext cx="5495925" cy="1000125"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>ReseDeleteDAO</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D38B1CDA-3073-4ABA-B96C-3E42E77E5286}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{54A5D636-AB10-4715-8904-91ADDD3CDB92}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1371600" y="1619250"/>
+          <a:ext cx="5486400" cy="4953000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>- reseDelete(postID : int) : String</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3380AA36-AADB-4F8C-91F2-C4A1579F6342}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="4772025"/>
+          <a:ext cx="5495925" cy="752475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>UserEntryServlet</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="四角形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3C7D925-E0FA-423E-8A2E-D3C0A5C2A2D6}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{3380AA36-AADB-4F8C-91F2-C4A1579F6342}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2047875" y="4505325"/>
+          <a:ext cx="5486400" cy="4876800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t># doGet(request : HttpServletRequest ,response :  HttpServletResponse) : void</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t># doPost(request : HttpServletRequest ,response :  HttpServletResponse) : void</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5D84A98-6CED-4E25-80D4-50DC6078116D}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{15723AC8-7A10-4908-982D-E38FEF435220}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1371600" y="1190625"/>
+          <a:ext cx="5495925" cy="1000125"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>PastGetDetailServlet</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BB9EC24-03FF-4D0C-8072-53366187CE54}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{E5D84A98-6CED-4E25-80D4-50DC6078116D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1371600" y="2190750"/>
+          <a:ext cx="5486400" cy="4953000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t># doGet(request : HttpServletRequest ,response :  HttpServletResponse) : void</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t># doPost(request : HttpServletRequest ,response :  HttpServletResponse) : void</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>5</xdr:row>
@@ -3168,7 +5682,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>PastGetServlet</a:t>
+            <a:t>PastGetAllServlet</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3582,7 +6096,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing22.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -3772,7 +6286,7 @@
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63C67BF2-7220-4136-B52E-D9403566D7C7}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{DC1057C7-FC07-4040-8025-E31AEDDF86B6}"/>
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{11E1D26F-E460-4ECA-9486-F5E2F70D12AA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3955,7 +6469,48 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>- pastGet(userID : int) : String</a:t>
+            <a:t>- pastGetAll(userID : int) : ArrayList&lt;PastInfo&gt;</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-pastGetDetail(userID : int, pastID : int) : ArrayList&lt;PastInfo&gt;</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -4117,7 +6672,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing23.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -4685,241 +7240,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="四角形 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3380AA36-AADB-4F8C-91F2-C4A1579F6342}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="685800" y="4772025"/>
-          <a:ext cx="5495925" cy="752475"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="l"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>UserEntryServlet</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="四角形 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3C7D925-E0FA-423E-8A2E-D3C0A5C2A2D6}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{3380AA36-AADB-4F8C-91F2-C4A1579F6342}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2047875" y="4505325"/>
-          <a:ext cx="5486400" cy="4876800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent2"/>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" indent="0" algn="l">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t># doGet(request : HttpServletRequest ,response :  HttpServletResponse) : void</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" marR="0" indent="0" algn="l">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t># doPost(request : HttpServletRequest ,response :  HttpServletResponse) : void</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr marL="0" indent="0" algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing24.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -7946,33 +10267,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B5:N18"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="5" spans="2:14" ht="76.5" x14ac:dyDescent="1.45">
+    <row r="5" spans="2:14" ht="76.5">
       <c r="B5" s="2"/>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:14">
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:14">
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:14">
       <c r="J9" s="7"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:14">
       <c r="J10" s="7"/>
       <c r="K10" s="5"/>
     </row>
-    <row r="11" spans="2:14" ht="167.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:14" ht="167.25" customHeight="1">
       <c r="J11" s="8"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
     </row>
-    <row r="18" spans="12:12" x14ac:dyDescent="0.4">
+    <row r="18" spans="12:12">
       <c r="L18" s="3"/>
     </row>
   </sheetData>
@@ -7987,9 +10308,9 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78133CEB-90F5-4068-ACFB-6FE720934B2F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FD3C0A3-5113-4CBF-B959-2D25BF0DAFA3}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData/>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7998,33 +10319,44 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78133CEB-90F5-4068-ACFB-6FE720934B2F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData/>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B11125D4-B752-43F8-B691-DE74B3DD65CB}">
   <dimension ref="C4:O10"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="4" spans="3:15" ht="76.5" x14ac:dyDescent="1.45">
+    <row r="4" spans="3:15" ht="76.5">
       <c r="C4" s="2"/>
     </row>
-    <row r="6" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="6" spans="3:15">
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="7" spans="3:15">
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="8" spans="3:15">
       <c r="K8" s="7"/>
       <c r="L8" s="4"/>
     </row>
-    <row r="9" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="9" spans="3:15">
       <c r="K9" s="7"/>
       <c r="L9" s="5"/>
     </row>
-    <row r="10" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="10" spans="3:15">
       <c r="K10" s="8"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8036,36 +10368,36 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{858A729A-A6CA-4A4B-B807-6CB200B4E071}">
   <dimension ref="C6:O72"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="6" spans="3:15" ht="76.5" x14ac:dyDescent="1.45">
+    <row r="6" spans="3:15" ht="76.5">
       <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="8" spans="3:15">
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="9" spans="3:15">
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="10" spans="3:15">
       <c r="K10" s="7"/>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="11" spans="3:15">
       <c r="K11" s="7"/>
       <c r="L11" s="5"/>
     </row>
-    <row r="12" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="12" spans="3:15">
       <c r="K12" s="8"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
     </row>
-    <row r="14" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="14" spans="3:15">
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
@@ -8075,7 +10407,7 @@
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="15" spans="3:15">
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
@@ -8085,7 +10417,7 @@
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
     </row>
-    <row r="16" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="16" spans="3:15">
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
@@ -8095,7 +10427,7 @@
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
     </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:10">
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
@@ -8105,7 +10437,7 @@
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
     </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:10">
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
@@ -8115,7 +10447,7 @@
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
     </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:10">
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
@@ -8125,7 +10457,7 @@
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
     </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:10">
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
@@ -8135,7 +10467,7 @@
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
     </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:10">
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
@@ -8145,7 +10477,7 @@
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
     </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:10">
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
@@ -8155,7 +10487,7 @@
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
     </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:10">
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
@@ -8165,7 +10497,7 @@
       <c r="I23" s="6"/>
       <c r="J23" s="6"/>
     </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:10">
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
@@ -8175,7 +10507,7 @@
       <c r="I24" s="6"/>
       <c r="J24" s="6"/>
     </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:10">
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
@@ -8185,7 +10517,7 @@
       <c r="I25" s="6"/>
       <c r="J25" s="6"/>
     </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:10">
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
@@ -8195,7 +10527,7 @@
       <c r="I26" s="6"/>
       <c r="J26" s="6"/>
     </row>
-    <row r="27" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:10">
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -8205,7 +10537,7 @@
       <c r="I27" s="6"/>
       <c r="J27" s="6"/>
     </row>
-    <row r="28" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:10">
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
@@ -8215,7 +10547,7 @@
       <c r="I28" s="6"/>
       <c r="J28" s="6"/>
     </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:10">
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
@@ -8225,7 +10557,7 @@
       <c r="I29" s="6"/>
       <c r="J29" s="6"/>
     </row>
-    <row r="30" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:10">
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
@@ -8235,7 +10567,7 @@
       <c r="I30" s="6"/>
       <c r="J30" s="6"/>
     </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:10">
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
@@ -8245,7 +10577,7 @@
       <c r="I31" s="6"/>
       <c r="J31" s="6"/>
     </row>
-    <row r="32" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:10">
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
@@ -8255,7 +10587,7 @@
       <c r="I32" s="6"/>
       <c r="J32" s="6"/>
     </row>
-    <row r="33" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:10">
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
@@ -8265,7 +10597,7 @@
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
     </row>
-    <row r="34" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:10">
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
@@ -8275,7 +10607,7 @@
       <c r="I34" s="6"/>
       <c r="J34" s="6"/>
     </row>
-    <row r="35" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:10">
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
@@ -8285,7 +10617,7 @@
       <c r="I35" s="6"/>
       <c r="J35" s="6"/>
     </row>
-    <row r="36" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:10">
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
@@ -8295,7 +10627,7 @@
       <c r="I36" s="6"/>
       <c r="J36" s="6"/>
     </row>
-    <row r="50" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="50" spans="3:10">
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
@@ -8305,7 +10637,7 @@
       <c r="I50" s="6"/>
       <c r="J50" s="6"/>
     </row>
-    <row r="51" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="51" spans="3:10">
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
@@ -8315,7 +10647,7 @@
       <c r="I51" s="6"/>
       <c r="J51" s="6"/>
     </row>
-    <row r="52" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="52" spans="3:10">
       <c r="C52" s="6"/>
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
@@ -8325,7 +10657,7 @@
       <c r="I52" s="6"/>
       <c r="J52" s="6"/>
     </row>
-    <row r="53" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="53" spans="3:10">
       <c r="C53" s="6"/>
       <c r="D53" s="6"/>
       <c r="E53" s="6"/>
@@ -8335,7 +10667,7 @@
       <c r="I53" s="6"/>
       <c r="J53" s="6"/>
     </row>
-    <row r="54" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="54" spans="3:10">
       <c r="C54" s="6"/>
       <c r="D54" s="6"/>
       <c r="E54" s="6"/>
@@ -8345,7 +10677,7 @@
       <c r="I54" s="6"/>
       <c r="J54" s="6"/>
     </row>
-    <row r="55" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="55" spans="3:10">
       <c r="C55" s="6"/>
       <c r="D55" s="6"/>
       <c r="E55" s="6"/>
@@ -8355,7 +10687,7 @@
       <c r="I55" s="6"/>
       <c r="J55" s="6"/>
     </row>
-    <row r="56" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="56" spans="3:10">
       <c r="C56" s="6"/>
       <c r="D56" s="6"/>
       <c r="E56" s="6"/>
@@ -8365,7 +10697,7 @@
       <c r="I56" s="6"/>
       <c r="J56" s="6"/>
     </row>
-    <row r="57" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="57" spans="3:10">
       <c r="C57" s="6"/>
       <c r="D57" s="6"/>
       <c r="E57" s="6"/>
@@ -8375,7 +10707,7 @@
       <c r="I57" s="6"/>
       <c r="J57" s="6"/>
     </row>
-    <row r="58" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="58" spans="3:10">
       <c r="C58" s="6"/>
       <c r="D58" s="6"/>
       <c r="E58" s="6"/>
@@ -8385,7 +10717,7 @@
       <c r="I58" s="6"/>
       <c r="J58" s="6"/>
     </row>
-    <row r="59" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="59" spans="3:10">
       <c r="C59" s="6"/>
       <c r="D59" s="6"/>
       <c r="E59" s="6"/>
@@ -8395,7 +10727,7 @@
       <c r="I59" s="6"/>
       <c r="J59" s="6"/>
     </row>
-    <row r="60" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="60" spans="3:10">
       <c r="C60" s="6"/>
       <c r="D60" s="6"/>
       <c r="E60" s="6"/>
@@ -8405,7 +10737,7 @@
       <c r="I60" s="6"/>
       <c r="J60" s="6"/>
     </row>
-    <row r="61" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="61" spans="3:10">
       <c r="C61" s="6"/>
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
@@ -8415,7 +10747,7 @@
       <c r="I61" s="6"/>
       <c r="J61" s="6"/>
     </row>
-    <row r="62" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="62" spans="3:10">
       <c r="C62" s="6"/>
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
@@ -8425,7 +10757,7 @@
       <c r="I62" s="6"/>
       <c r="J62" s="6"/>
     </row>
-    <row r="63" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="63" spans="3:10">
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
@@ -8435,7 +10767,7 @@
       <c r="I63" s="6"/>
       <c r="J63" s="6"/>
     </row>
-    <row r="64" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="64" spans="3:10">
       <c r="C64" s="6"/>
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
@@ -8445,7 +10777,7 @@
       <c r="I64" s="6"/>
       <c r="J64" s="6"/>
     </row>
-    <row r="65" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="65" spans="3:10">
       <c r="C65" s="6"/>
       <c r="D65" s="6"/>
       <c r="E65" s="6"/>
@@ -8455,7 +10787,7 @@
       <c r="I65" s="6"/>
       <c r="J65" s="6"/>
     </row>
-    <row r="66" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="66" spans="3:10">
       <c r="C66" s="6"/>
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
@@ -8465,7 +10797,7 @@
       <c r="I66" s="6"/>
       <c r="J66" s="6"/>
     </row>
-    <row r="67" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="67" spans="3:10">
       <c r="C67" s="6"/>
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
@@ -8475,7 +10807,7 @@
       <c r="I67" s="6"/>
       <c r="J67" s="6"/>
     </row>
-    <row r="68" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="68" spans="3:10">
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
@@ -8485,7 +10817,7 @@
       <c r="I68" s="6"/>
       <c r="J68" s="6"/>
     </row>
-    <row r="69" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="69" spans="3:10">
       <c r="C69" s="6"/>
       <c r="D69" s="6"/>
       <c r="E69" s="6"/>
@@ -8495,7 +10827,7 @@
       <c r="I69" s="6"/>
       <c r="J69" s="6"/>
     </row>
-    <row r="70" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="70" spans="3:10">
       <c r="C70" s="6"/>
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
@@ -8505,7 +10837,7 @@
       <c r="I70" s="6"/>
       <c r="J70" s="6"/>
     </row>
-    <row r="71" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="71" spans="3:10">
       <c r="C71" s="6"/>
       <c r="D71" s="6"/>
       <c r="E71" s="6"/>
@@ -8515,7 +10847,7 @@
       <c r="I71" s="6"/>
       <c r="J71" s="6"/>
     </row>
-    <row r="72" spans="3:10" x14ac:dyDescent="0.4">
+    <row r="72" spans="3:10">
       <c r="C72" s="6"/>
       <c r="D72" s="6"/>
       <c r="E72" s="6"/>
@@ -8535,73 +10867,34 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5B3922A-DE08-4624-85AF-BA1C397B81ED}">
   <dimension ref="C5:O11"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="5" spans="3:15" ht="76.5" x14ac:dyDescent="1.45">
+    <row r="5" spans="3:15" ht="76.5">
       <c r="C5" s="2"/>
     </row>
-    <row r="7" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="7" spans="3:15">
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="8" spans="3:15">
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="9" spans="3:15">
       <c r="K9" s="7"/>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="10" spans="3:15">
       <c r="K10" s="7"/>
       <c r="L10" s="5"/>
     </row>
-    <row r="11" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="11" spans="3:15">
       <c r="K11" s="8"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="L11:O11"/>
-  </mergeCells>
-  <phoneticPr fontId="8"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10DEA0A2-812B-4FDB-84DE-0116CCE25969}">
-  <dimension ref="C5:O11"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData>
-    <row r="5" spans="3:15" ht="76.5" x14ac:dyDescent="1.45">
-      <c r="C5" s="2"/>
-    </row>
-    <row r="7" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="K7" s="1"/>
-    </row>
-    <row r="8" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="K8" s="1"/>
-    </row>
-    <row r="9" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="K9" s="7"/>
-      <c r="L9" s="4"/>
-    </row>
-    <row r="10" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="K10" s="7"/>
-      <c r="L10" s="5"/>
-    </row>
-    <row r="11" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="K11" s="8"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8614,33 +10907,72 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10DEA0A2-812B-4FDB-84DE-0116CCE25969}">
+  <dimension ref="C5:O11"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData>
+    <row r="5" spans="3:15" ht="76.5">
+      <c r="C5" s="2"/>
+    </row>
+    <row r="7" spans="3:15">
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="3:15">
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="3:15">
+      <c r="K9" s="7"/>
+      <c r="L9" s="4"/>
+    </row>
+    <row r="10" spans="3:15">
+      <c r="K10" s="7"/>
+      <c r="L10" s="5"/>
+    </row>
+    <row r="11" spans="3:15">
+      <c r="K11" s="8"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="L11:O11"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{308217FA-2716-4596-888D-BA716CD6B1EA}">
   <dimension ref="C11:O17"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="11" spans="3:12" ht="76.5" x14ac:dyDescent="1.45">
+    <row r="11" spans="3:12" ht="76.5">
       <c r="C11" s="2"/>
     </row>
-    <row r="13" spans="3:12" x14ac:dyDescent="0.4">
+    <row r="13" spans="3:12">
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="3:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="3:12">
       <c r="K14" s="1"/>
     </row>
-    <row r="15" spans="3:12" x14ac:dyDescent="0.4">
+    <row r="15" spans="3:12">
       <c r="K15" s="7"/>
       <c r="L15" s="4"/>
     </row>
-    <row r="16" spans="3:12" x14ac:dyDescent="0.4">
+    <row r="16" spans="3:12">
       <c r="K16" s="7"/>
       <c r="L16" s="5"/>
     </row>
-    <row r="17" spans="11:15" x14ac:dyDescent="0.4">
+    <row r="17" spans="11:15">
       <c r="K17" s="8"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8652,34 +10984,34 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{540AFABB-2284-4628-8404-881C4DF8BBF3}">
   <dimension ref="C5:O11"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="5" spans="3:15" ht="76.5" x14ac:dyDescent="1.45">
+    <row r="5" spans="3:15" ht="76.5">
       <c r="C5" s="2"/>
     </row>
-    <row r="7" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="7" spans="3:15">
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="8" spans="3:15">
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="K9" s="9"/>
+    <row r="9" spans="3:15">
+      <c r="K9" s="7"/>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="K10" s="9"/>
+    <row r="10" spans="3:15">
+      <c r="K10" s="7"/>
       <c r="L10" s="5"/>
     </row>
-    <row r="11" spans="3:15" x14ac:dyDescent="0.4">
-      <c r="K11" s="10"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
+    <row r="11" spans="3:15">
+      <c r="K11" s="8"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8691,34 +11023,34 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB7F4A5D-207A-4B36-B738-BEB15FAA9B9E}">
   <dimension ref="C2:O8"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="2" spans="3:15" ht="76.5" x14ac:dyDescent="1.45">
+    <row r="2" spans="3:15" ht="76.5">
       <c r="C2" s="2"/>
     </row>
-    <row r="4" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="4" spans="3:15">
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="5" spans="3:15">
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="6" spans="3:15">
       <c r="K6" s="7"/>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="7" spans="3:15">
       <c r="K7" s="7"/>
       <c r="L7" s="5"/>
     </row>
-    <row r="8" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="8" spans="3:15">
       <c r="K8" s="8"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8730,23 +11062,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33CAEAB3-C628-4BC9-89D5-C319D5D6D56E}">
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7473C3D6-B659-4883-BF51-DBFCC52FE8C3}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <sheetData/>
-  <phoneticPr fontId="8"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5766E920-903E-4921-8766-22428B5C9340}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
-  <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -8755,31 +11075,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEDFCAFA-3C5F-4B4A-885A-49160B0C26B3}">
   <dimension ref="C5:O11"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="5" spans="3:15" ht="76.5" x14ac:dyDescent="1.45">
+    <row r="5" spans="3:15" ht="76.5">
       <c r="C5" s="2"/>
     </row>
-    <row r="7" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="7" spans="3:15">
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="8" spans="3:15">
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="9" spans="3:15">
       <c r="K9" s="7"/>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="10" spans="3:15">
       <c r="K10" s="7"/>
       <c r="L10" s="5"/>
     </row>
-    <row r="11" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="11" spans="3:15">
       <c r="K11" s="8"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8792,9 +11112,29 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A44728-ABF2-406D-A40F-28A8A34E53C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2984243-B158-41BC-B9B1-8B535C7DE8F4}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1555C93-49D8-4C5B-8260-3BEDAADFC36B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9F465F7-9868-4383-8863-CFAD47356EAC}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <sheetData/>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8802,10 +11142,43 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33CAEAB3-C628-4BC9-89D5-C319D5D6D56E}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData/>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5766E920-903E-4921-8766-22428B5C9340}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData/>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A44728-ABF2-406D-A40F-28A8A34E53C1}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData/>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D621F75-B6A4-4A63-89AA-FBEF3C1D235F}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData/>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8816,31 +11189,31 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7027D6D-8678-4A17-A748-A2602CED5D96}">
   <dimension ref="C5:O11"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="5" spans="3:15" ht="76.5" x14ac:dyDescent="1.45">
+    <row r="5" spans="3:15" ht="76.5">
       <c r="C5" s="2"/>
     </row>
-    <row r="7" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="7" spans="3:15">
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="8" spans="3:15">
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="9" spans="3:15">
       <c r="K9" s="7"/>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="10" spans="3:15">
       <c r="K10" s="7"/>
       <c r="L10" s="5"/>
     </row>
-    <row r="11" spans="3:15" x14ac:dyDescent="0.4">
+    <row r="11" spans="3:15">
       <c r="K11" s="8"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8855,9 +11228,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8490CDFA-2546-463C-90A0-18885C56ABAA}">
   <dimension ref="N32"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
-    <row r="32" spans="14:14" x14ac:dyDescent="0.4">
+    <row r="32" spans="14:14">
       <c r="N32" t="s">
         <v>0</v>
       </c>
@@ -8873,7 +11246,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC68DF99-D275-42D8-AC3D-5F39E4F0D807}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData/>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8884,7 +11257,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC9E5CE7-CA29-4CA5-ACD0-77D3780DBEA5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData/>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8895,7 +11268,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9BE7919-1571-48B4-B6DF-A5A461474F69}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData/>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8904,22 +11277,20 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{501A6857-FA5F-48B7-8D8B-8C82CE0FD622}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0551D002-0E52-4B17-B3EF-4D5BAF7FD271}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <sheetData/>
-  <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FD3C0A3-5113-4CBF-B959-2D25BF0DAFA3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{501A6857-FA5F-48B7-8D8B-8C82CE0FD622}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData/>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/class_diagram/users/クラス図_面談予約sys (users)_最新.xlsx
+++ b/class_diagram/users/クラス図_面談予約sys (users)_最新.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ktc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{DDC5F448-C290-4053-AF89-2C5F4DE0E5F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C72D9F3-5572-446B-8968-DAF69F875519}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{DDC5F448-C290-4053-AF89-2C5F4DE0E5F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19934BFF-BE7A-41D8-9B45-42D3196BAEB8}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18945" windowHeight="11190" firstSheet="18" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18945" windowHeight="11190" firstSheet="21" activeTab="29" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="controller.UserPreServlet" sheetId="1" r:id="rId1"/>
@@ -39,6 +39,10 @@
     <sheet name="dao.PastGetDAO" sheetId="22" r:id="rId24"/>
     <sheet name="controller.EmailSendPreServlet" sheetId="23" r:id="rId25"/>
     <sheet name="dao.EmailCheckDAO" sheetId="24" r:id="rId26"/>
+    <sheet name="dao.StatusGetDAO" sheetId="32" r:id="rId27"/>
+    <sheet name="controller.StatusGetServlet" sheetId="33" r:id="rId28"/>
+    <sheet name="controller.WeeksGet" sheetId="34" r:id="rId29"/>
+    <sheet name="controller.DatesGet" sheetId="35" r:id="rId30"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -7629,6 +7633,2202 @@
             </a:solidFill>
             <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
           </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing25.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B167DCDC-7C12-4973-BF6B-B50D67C51EE7}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{15723AC8-7A10-4908-982D-E38FEF435220}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1371600" y="800100"/>
+          <a:ext cx="5495925" cy="847725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>StatusGetDAO</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3ECBA4BE-DEBD-4007-826A-77989BED3754}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{B167DCDC-7C12-4973-BF6B-B50D67C51EE7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1362075" y="1476375"/>
+          <a:ext cx="5486400" cy="4152900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>- getStatus(dates : ArrayList&lt;LocalDate&gt;) : ArrayList&lt;String&gt;</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing26.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{846DDE59-C8F1-4378-9518-19D8C521E839}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{15723AC8-7A10-4908-982D-E38FEF435220}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1371600" y="800100"/>
+          <a:ext cx="5495925" cy="847725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>StatusGetServlet</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{868A0325-DC00-454B-9AFD-35FD3791169A}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{846DDE59-C8F1-4378-9518-19D8C521E839}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1362075" y="1476375"/>
+          <a:ext cx="5486400" cy="4152900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-lt"/>
+            <a:cs typeface="+mn-lt"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-lt"/>
+              <a:cs typeface="+mn-lt"/>
+            </a:rPr>
+            <a:t># doGet(request : HttpServletRequest ,response :  HttpServletResponse) : void</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-lt"/>
+            <a:cs typeface="+mn-lt"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-lt"/>
+              <a:cs typeface="+mn-lt"/>
+            </a:rPr>
+            <a:t># doPost(request : HttpServletRequest ,response :  HttpServletResponse) : void</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing27.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C1FCEB0-4A05-461F-993E-DA01BC2676A0}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{15723AC8-7A10-4908-982D-E38FEF435220}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1371600" y="800100"/>
+          <a:ext cx="5495925" cy="847725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>WeeksGet</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B889F2CE-7CA8-416D-8EEC-A5FC9B563F34}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{9C1FCEB0-4A05-461F-993E-DA01BC2676A0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1362075" y="1476375"/>
+          <a:ext cx="5486400" cy="4152900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-lt"/>
+            <a:cs typeface="+mn-lt"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>- getWeeks(todayWeek : DayOfWeek) : ArrayList&lt;String&gt;</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing28.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62D721A1-14B6-419C-825A-BB043EBCFB7A}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{15723AC8-7A10-4908-982D-E38FEF435220}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1371600" y="800100"/>
+          <a:ext cx="5495925" cy="847725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>DatesGet</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3C818FB-7A98-4946-B7AF-AFB57A8B959D}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{62D721A1-14B6-419C-825A-BB043EBCFB7A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1362075" y="1476375"/>
+          <a:ext cx="5486400" cy="4152900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>- getDates(today : LocalDate) : ArrayList&lt;LocalDate&gt;</a:t>
+          </a:r>
         </a:p>
         <a:p>
           <a:pPr marL="0" marR="0" indent="0" algn="l">
@@ -11186,6 +13386,39 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A132E543-2CC7-4800-B3E9-A1B4345EB203}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{162AA59B-CAC8-4B3C-8F31-2455B8C88E34}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B6B4758-7A84-47A0-BA34-81FBCD200257}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7027D6D-8678-4A17-A748-A2602CED5D96}">
   <dimension ref="C5:O11"/>
@@ -11220,6 +13453,17 @@
     <mergeCell ref="L11:O11"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4F506AF-BC37-4BE1-9D8C-71052C40479A}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
